--- a/backend/data/financials_by_company/1751.HK.xlsx
+++ b/backend/data/financials_by_company/1751.HK.xlsx
@@ -652,558 +652,558 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>536415</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>12616000</v>
+        <v>-29595000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2820000</v>
+        <v>3251000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2820000</v>
+        <v>3251000</v>
       </c>
       <c r="G2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="H2" t="n">
-        <v>8319000</v>
+        <v>13700000</v>
       </c>
       <c r="I2" t="n">
-        <v>65226000</v>
+        <v>115538000</v>
       </c>
       <c r="J2" t="n">
-        <v>9796000</v>
+        <v>-26344000</v>
       </c>
       <c r="K2" t="n">
-        <v>1477000</v>
+        <v>-40044000</v>
       </c>
       <c r="L2" t="n">
-        <v>-168000</v>
+        <v>-835000</v>
       </c>
       <c r="M2" t="n">
-        <v>982000</v>
+        <v>860000</v>
       </c>
       <c r="N2" t="n">
-        <v>814000</v>
+        <v>25000</v>
       </c>
       <c r="O2" t="n">
-        <v>3315000</v>
+        <v>-43717585</v>
       </c>
       <c r="P2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="Q2" t="n">
-        <v>93820000</v>
+        <v>145082000</v>
       </c>
       <c r="R2" t="n">
-        <v>1477000</v>
+        <v>-40044000</v>
       </c>
       <c r="S2" t="n">
-        <v>243052230</v>
+        <v>190925521</v>
       </c>
       <c r="T2" t="n">
-        <v>243052230</v>
+        <v>190925521</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001991</v>
+        <v>-0.214903</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001991</v>
+        <v>-0.214903</v>
       </c>
       <c r="W2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="X2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="AA2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="AB2" t="n">
-        <v>495000</v>
+        <v>-41003000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="AD2" t="n">
-        <v>495000</v>
+        <v>-40904000</v>
       </c>
       <c r="AE2" t="n">
-        <v>176000</v>
+        <v>89000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2820000</v>
+        <v>3251000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-911000</v>
+        <v>-401000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3731000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-5446000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2596000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-168000</v>
+        <v>-835000</v>
       </c>
       <c r="AK2" t="n">
-        <v>982000</v>
+        <v>860000</v>
       </c>
       <c r="AL2" t="n">
-        <v>814000</v>
+        <v>25000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3307000</v>
+        <v>-43409000</v>
       </c>
       <c r="AN2" t="n">
-        <v>28594000</v>
+        <v>29544000</v>
       </c>
       <c r="AO2" t="n">
-        <v>28844000</v>
+        <v>29899000</v>
       </c>
       <c r="AP2" t="n">
-        <v>28844000</v>
+        <v>29899000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>31901000</v>
+        <v>-13865000</v>
       </c>
       <c r="AR2" t="n">
-        <v>65226000</v>
+        <v>115538000</v>
       </c>
       <c r="AS2" t="n">
-        <v>97127000</v>
+        <v>101673000</v>
       </c>
       <c r="AT2" t="n">
-        <v>97127000</v>
+        <v>101673000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-40157.218443</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.024727</v>
       </c>
       <c r="D3" t="n">
-        <v>11088000</v>
+        <v>5298000</v>
       </c>
       <c r="E3" t="n">
-        <v>802000</v>
+        <v>-1624000</v>
       </c>
       <c r="F3" t="n">
-        <v>802000</v>
+        <v>-1624000</v>
       </c>
       <c r="G3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="H3" t="n">
-        <v>9460000</v>
+        <v>12066000</v>
       </c>
       <c r="I3" t="n">
-        <v>91726000</v>
+        <v>58973000</v>
       </c>
       <c r="J3" t="n">
-        <v>11890000</v>
+        <v>3674000</v>
       </c>
       <c r="K3" t="n">
-        <v>2430000</v>
+        <v>-8392000</v>
       </c>
       <c r="L3" t="n">
-        <v>-783000</v>
+        <v>-858000</v>
       </c>
       <c r="M3" t="n">
-        <v>1112000</v>
+        <v>869000</v>
       </c>
       <c r="N3" t="n">
-        <v>329000</v>
+        <v>11000</v>
       </c>
       <c r="O3" t="n">
-        <v>516000</v>
+        <v>-7448157.218443</v>
       </c>
       <c r="P3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="Q3" t="n">
-        <v>120136000</v>
+        <v>82476000</v>
       </c>
       <c r="R3" t="n">
-        <v>2430000</v>
+        <v>-8392000</v>
       </c>
       <c r="S3" t="n">
-        <v>233418352</v>
+        <v>222843088</v>
       </c>
       <c r="T3" t="n">
-        <v>233418352</v>
+        <v>222843088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005673</v>
+        <v>-0.04051</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005673</v>
+        <v>-0.04051</v>
       </c>
       <c r="W3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="X3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1318000</v>
+        <v>-9032000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-229000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1318000</v>
+        <v>-9261000</v>
       </c>
       <c r="AE3" t="n">
-        <v>249000</v>
+        <v>35000</v>
       </c>
       <c r="AF3" t="n">
-        <v>802000</v>
+        <v>-1624000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-24000</v>
+        <v>-160000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-778000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>1784000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>-783000</v>
+        <v>-858000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1112000</v>
+        <v>869000</v>
       </c>
       <c r="AL3" t="n">
-        <v>329000</v>
+        <v>11000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1050000</v>
+        <v>-6814000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28410000</v>
+        <v>23503000</v>
       </c>
       <c r="AO3" t="n">
-        <v>28490000</v>
+        <v>25068000</v>
       </c>
       <c r="AP3" t="n">
-        <v>28490000</v>
+        <v>25068000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>29460000</v>
+        <v>16689000</v>
       </c>
       <c r="AR3" t="n">
-        <v>91726000</v>
+        <v>58973000</v>
       </c>
       <c r="AS3" t="n">
-        <v>121186000</v>
+        <v>75662000</v>
       </c>
       <c r="AT3" t="n">
-        <v>121186000</v>
+        <v>75662000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-40157.218443</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.024727</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5298000</v>
+        <v>11088000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1624000</v>
+        <v>802000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1624000</v>
+        <v>802000</v>
       </c>
       <c r="G4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="H4" t="n">
-        <v>12066000</v>
+        <v>9460000</v>
       </c>
       <c r="I4" t="n">
-        <v>58973000</v>
+        <v>91726000</v>
       </c>
       <c r="J4" t="n">
-        <v>3674000</v>
+        <v>11890000</v>
       </c>
       <c r="K4" t="n">
-        <v>-8392000</v>
+        <v>2430000</v>
       </c>
       <c r="L4" t="n">
-        <v>-858000</v>
+        <v>-783000</v>
       </c>
       <c r="M4" t="n">
-        <v>869000</v>
+        <v>1112000</v>
       </c>
       <c r="N4" t="n">
-        <v>11000</v>
+        <v>329000</v>
       </c>
       <c r="O4" t="n">
-        <v>-7448157.218443</v>
+        <v>516000</v>
       </c>
       <c r="P4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="Q4" t="n">
-        <v>82476000</v>
+        <v>120136000</v>
       </c>
       <c r="R4" t="n">
-        <v>-8392000</v>
+        <v>2430000</v>
       </c>
       <c r="S4" t="n">
-        <v>222843088</v>
+        <v>233418352</v>
       </c>
       <c r="T4" t="n">
-        <v>222843088</v>
+        <v>233418352</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04051</v>
+        <v>0.005673</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.04051</v>
+        <v>0.005673</v>
       </c>
       <c r="W4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="X4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-9032000</v>
+        <v>1318000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-229000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-9261000</v>
+        <v>1318000</v>
       </c>
       <c r="AE4" t="n">
-        <v>35000</v>
+        <v>249000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1624000</v>
+        <v>802000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-160000</v>
+        <v>-24000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1784000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>-778000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-858000</v>
+        <v>-783000</v>
       </c>
       <c r="AK4" t="n">
-        <v>869000</v>
+        <v>1112000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11000</v>
+        <v>329000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-6814000</v>
+        <v>1050000</v>
       </c>
       <c r="AN4" t="n">
-        <v>23503000</v>
+        <v>28410000</v>
       </c>
       <c r="AO4" t="n">
-        <v>25068000</v>
+        <v>28490000</v>
       </c>
       <c r="AP4" t="n">
-        <v>25068000</v>
+        <v>28490000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16689000</v>
+        <v>29460000</v>
       </c>
       <c r="AR4" t="n">
-        <v>58973000</v>
+        <v>91726000</v>
       </c>
       <c r="AS4" t="n">
-        <v>75662000</v>
+        <v>121186000</v>
       </c>
       <c r="AT4" t="n">
-        <v>75662000</v>
+        <v>121186000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>536415</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-29595000</v>
+        <v>12616000</v>
       </c>
       <c r="E5" t="n">
-        <v>3251000</v>
+        <v>-2820000</v>
       </c>
       <c r="F5" t="n">
-        <v>3251000</v>
+        <v>-2820000</v>
       </c>
       <c r="G5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="H5" t="n">
-        <v>13700000</v>
+        <v>8319000</v>
       </c>
       <c r="I5" t="n">
-        <v>115538000</v>
+        <v>65226000</v>
       </c>
       <c r="J5" t="n">
-        <v>-26344000</v>
+        <v>9796000</v>
       </c>
       <c r="K5" t="n">
-        <v>-40044000</v>
+        <v>1477000</v>
       </c>
       <c r="L5" t="n">
-        <v>-835000</v>
+        <v>-168000</v>
       </c>
       <c r="M5" t="n">
-        <v>860000</v>
+        <v>982000</v>
       </c>
       <c r="N5" t="n">
-        <v>25000</v>
+        <v>814000</v>
       </c>
       <c r="O5" t="n">
-        <v>-43717585</v>
+        <v>3315000</v>
       </c>
       <c r="P5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="Q5" t="n">
-        <v>145082000</v>
+        <v>93820000</v>
       </c>
       <c r="R5" t="n">
-        <v>-40044000</v>
+        <v>1477000</v>
       </c>
       <c r="S5" t="n">
-        <v>190925521</v>
+        <v>243052230</v>
       </c>
       <c r="T5" t="n">
-        <v>190925521</v>
+        <v>243052230</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.214903</v>
+        <v>0.001991</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.214903</v>
+        <v>0.001991</v>
       </c>
       <c r="W5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="X5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-41003000</v>
+        <v>495000</v>
       </c>
       <c r="AC5" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-40904000</v>
+        <v>495000</v>
       </c>
       <c r="AE5" t="n">
-        <v>89000</v>
+        <v>176000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3251000</v>
+        <v>-2820000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-401000</v>
+        <v>-911000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5446000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2596000</v>
-      </c>
+        <v>3731000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-835000</v>
+        <v>-168000</v>
       </c>
       <c r="AK5" t="n">
-        <v>860000</v>
+        <v>982000</v>
       </c>
       <c r="AL5" t="n">
-        <v>25000</v>
+        <v>814000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-43409000</v>
+        <v>3307000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29544000</v>
+        <v>28594000</v>
       </c>
       <c r="AO5" t="n">
-        <v>29899000</v>
+        <v>28844000</v>
       </c>
       <c r="AP5" t="n">
-        <v>29899000</v>
+        <v>28844000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-13865000</v>
+        <v>31901000</v>
       </c>
       <c r="AR5" t="n">
-        <v>115538000</v>
+        <v>65226000</v>
       </c>
       <c r="AS5" t="n">
-        <v>101673000</v>
+        <v>97127000</v>
       </c>
       <c r="AT5" t="n">
-        <v>101673000</v>
+        <v>97127000</v>
       </c>
     </row>
   </sheetData>
@@ -1479,618 +1479,618 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>243052230</v>
+        <v>207507042</v>
       </c>
       <c r="C2" t="n">
-        <v>243052230</v>
+        <v>207507042</v>
       </c>
       <c r="D2" t="n">
-        <v>2304000</v>
+        <v>10473000</v>
       </c>
       <c r="E2" t="n">
-        <v>17101000</v>
+        <v>19922000</v>
       </c>
       <c r="F2" t="n">
-        <v>23880000</v>
+        <v>17295000</v>
       </c>
       <c r="G2" t="n">
-        <v>34704000</v>
+        <v>28267000</v>
       </c>
       <c r="H2" t="n">
-        <v>16510000</v>
+        <v>-2555000</v>
       </c>
       <c r="I2" t="n">
-        <v>23880000</v>
+        <v>17295000</v>
       </c>
       <c r="J2" t="n">
-        <v>6277000</v>
+        <v>8950000</v>
       </c>
       <c r="K2" t="n">
-        <v>23880000</v>
+        <v>17295000</v>
       </c>
       <c r="L2" t="n">
-        <v>23880000</v>
+        <v>17809000</v>
       </c>
       <c r="M2" t="n">
-        <v>23880000</v>
+        <v>17295000</v>
       </c>
       <c r="N2" t="n">
-        <v>23880000</v>
+        <v>17295000</v>
       </c>
       <c r="O2" t="n">
-        <v>-78876000</v>
+        <v>-71657000</v>
       </c>
       <c r="P2" t="n">
-        <v>74347000</v>
+        <v>64575000</v>
       </c>
       <c r="Q2" t="n">
-        <v>12096000</v>
+        <v>8064000</v>
       </c>
       <c r="R2" t="n">
-        <v>12096000</v>
+        <v>8064000</v>
       </c>
       <c r="S2" t="n">
-        <v>38027000</v>
+        <v>57160000</v>
       </c>
       <c r="T2" t="n">
-        <v>3140000</v>
+        <v>5139000</v>
       </c>
       <c r="U2" t="n">
-        <v>690000</v>
+        <v>818000</v>
       </c>
       <c r="V2" t="n">
-        <v>650000</v>
+        <v>80000</v>
       </c>
       <c r="W2" t="n">
-        <v>1800000</v>
+        <v>4241000</v>
       </c>
       <c r="X2" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>3727000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>514000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>34887000</v>
+        <v>52021000</v>
       </c>
       <c r="AA2" t="n">
-        <v>15301000</v>
+        <v>15681000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4477000</v>
+        <v>5223000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10824000</v>
+        <v>10458000</v>
       </c>
       <c r="AD2" t="n">
-        <v>12594000</v>
+        <v>21112000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2612000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>3657000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>342000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>9982000</v>
+        <v>17113000</v>
       </c>
       <c r="AH2" t="n">
-        <v>61907000</v>
+        <v>74455000</v>
       </c>
       <c r="AI2" t="n">
-        <v>10510000</v>
+        <v>24989000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10510000</v>
+        <v>24989000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-87368000</v>
+        <v>-65257000</v>
       </c>
       <c r="AL2" t="n">
-        <v>97878000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>90246000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>24989000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>91144000</v>
+        <v>84468000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6734000</v>
+        <v>5778000</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>51397000</v>
+        <v>49466000</v>
       </c>
       <c r="AR2" t="n">
-        <v>15259000</v>
+        <v>14559000</v>
       </c>
       <c r="AS2" t="n">
-        <v>21528000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>20580000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>113000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>6090000</v>
+        <v>13715000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-5399000</v>
+        <v>-5420000</v>
       </c>
       <c r="AW2" t="n">
-        <v>11489000</v>
+        <v>19135000</v>
       </c>
       <c r="AX2" t="n">
-        <v>8520000</v>
+        <v>499000</v>
       </c>
       <c r="AY2" t="n">
-        <v>8520000</v>
+        <v>499000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8520000</v>
+        <v>499000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>243052230</v>
+        <v>207507042</v>
       </c>
       <c r="C3" t="n">
-        <v>243052230</v>
+        <v>207507042</v>
       </c>
       <c r="D3" t="n">
-        <v>501000</v>
+        <v>12064000</v>
       </c>
       <c r="E3" t="n">
-        <v>20478000</v>
+        <v>23689000</v>
       </c>
       <c r="F3" t="n">
-        <v>23385000</v>
+        <v>8263000</v>
       </c>
       <c r="G3" t="n">
-        <v>35768000</v>
+        <v>23890000</v>
       </c>
       <c r="H3" t="n">
-        <v>15004000</v>
+        <v>-3890000</v>
       </c>
       <c r="I3" t="n">
-        <v>23385000</v>
+        <v>8263000</v>
       </c>
       <c r="J3" t="n">
-        <v>8095000</v>
+        <v>8062000</v>
       </c>
       <c r="K3" t="n">
-        <v>23385000</v>
+        <v>8263000</v>
       </c>
       <c r="L3" t="n">
-        <v>23385000</v>
+        <v>8263000</v>
       </c>
       <c r="M3" t="n">
-        <v>23385000</v>
+        <v>8263000</v>
       </c>
       <c r="N3" t="n">
-        <v>23385000</v>
+        <v>8263000</v>
       </c>
       <c r="O3" t="n">
-        <v>-79371000</v>
+        <v>-80689000</v>
       </c>
       <c r="P3" t="n">
-        <v>74347000</v>
+        <v>64575000</v>
       </c>
       <c r="Q3" t="n">
-        <v>12096000</v>
+        <v>8064000</v>
       </c>
       <c r="R3" t="n">
-        <v>12096000</v>
+        <v>8064000</v>
       </c>
       <c r="S3" t="n">
-        <v>48078000</v>
+        <v>52543000</v>
       </c>
       <c r="T3" t="n">
-        <v>4587000</v>
+        <v>5159000</v>
       </c>
       <c r="U3" t="n">
-        <v>742000</v>
+        <v>727000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3845000</v>
+        <v>4432000</v>
       </c>
       <c r="X3" t="n">
-        <v>3845000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>4432000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>43491000</v>
+        <v>47384000</v>
       </c>
       <c r="AA3" t="n">
-        <v>16633000</v>
+        <v>19257000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4250000</v>
+        <v>3630000</v>
       </c>
       <c r="AC3" t="n">
-        <v>12383000</v>
+        <v>15627000</v>
       </c>
       <c r="AD3" t="n">
-        <v>19967000</v>
+        <v>17543000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3613000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>3962000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="n">
-        <v>16354000</v>
+        <v>13581000</v>
       </c>
       <c r="AH3" t="n">
-        <v>71463000</v>
+        <v>60806000</v>
       </c>
       <c r="AI3" t="n">
-        <v>12968000</v>
+        <v>17312000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12968000</v>
+        <v>17312000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-80389000</v>
+        <v>-73750000</v>
       </c>
       <c r="AL3" t="n">
-        <v>93357000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>91062000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>17312000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>86623000</v>
+        <v>84176000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6734000</v>
+        <v>6886000</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>58495000</v>
+        <v>43494000</v>
       </c>
       <c r="AR3" t="n">
-        <v>14757000</v>
+        <v>14570000</v>
       </c>
       <c r="AS3" t="n">
-        <v>22935000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>17885000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="n">
-        <v>8921000</v>
+        <v>7476000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-5220000</v>
+        <v>-5618000</v>
       </c>
       <c r="AW3" t="n">
-        <v>14141000</v>
+        <v>13094000</v>
       </c>
       <c r="AX3" t="n">
-        <v>11882000</v>
+        <v>3563000</v>
       </c>
       <c r="AY3" t="n">
-        <v>11882000</v>
+        <v>3563000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11882000</v>
+        <v>3563000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>207507042</v>
+        <v>243052230</v>
       </c>
       <c r="C4" t="n">
-        <v>207507042</v>
+        <v>243052230</v>
       </c>
       <c r="D4" t="n">
-        <v>12064000</v>
+        <v>501000</v>
       </c>
       <c r="E4" t="n">
-        <v>23689000</v>
+        <v>20478000</v>
       </c>
       <c r="F4" t="n">
-        <v>8263000</v>
+        <v>23385000</v>
       </c>
       <c r="G4" t="n">
-        <v>23890000</v>
+        <v>35768000</v>
       </c>
       <c r="H4" t="n">
-        <v>-3890000</v>
+        <v>15004000</v>
       </c>
       <c r="I4" t="n">
-        <v>8263000</v>
+        <v>23385000</v>
       </c>
       <c r="J4" t="n">
-        <v>8062000</v>
+        <v>8095000</v>
       </c>
       <c r="K4" t="n">
-        <v>8263000</v>
+        <v>23385000</v>
       </c>
       <c r="L4" t="n">
-        <v>8263000</v>
+        <v>23385000</v>
       </c>
       <c r="M4" t="n">
-        <v>8263000</v>
+        <v>23385000</v>
       </c>
       <c r="N4" t="n">
-        <v>8263000</v>
+        <v>23385000</v>
       </c>
       <c r="O4" t="n">
-        <v>-80689000</v>
+        <v>-79371000</v>
       </c>
       <c r="P4" t="n">
-        <v>64575000</v>
+        <v>74347000</v>
       </c>
       <c r="Q4" t="n">
-        <v>8064000</v>
+        <v>12096000</v>
       </c>
       <c r="R4" t="n">
-        <v>8064000</v>
+        <v>12096000</v>
       </c>
       <c r="S4" t="n">
-        <v>52543000</v>
+        <v>48078000</v>
       </c>
       <c r="T4" t="n">
-        <v>5159000</v>
+        <v>4587000</v>
       </c>
       <c r="U4" t="n">
-        <v>727000</v>
+        <v>742000</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4432000</v>
+        <v>3845000</v>
       </c>
       <c r="X4" t="n">
-        <v>4432000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>3845000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>47384000</v>
+        <v>43491000</v>
       </c>
       <c r="AA4" t="n">
-        <v>19257000</v>
+        <v>16633000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3630000</v>
+        <v>4250000</v>
       </c>
       <c r="AC4" t="n">
-        <v>15627000</v>
+        <v>12383000</v>
       </c>
       <c r="AD4" t="n">
-        <v>17543000</v>
+        <v>19967000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3962000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
+        <v>3613000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>13581000</v>
+        <v>16354000</v>
       </c>
       <c r="AH4" t="n">
-        <v>60806000</v>
+        <v>71463000</v>
       </c>
       <c r="AI4" t="n">
-        <v>17312000</v>
+        <v>12968000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17312000</v>
+        <v>12968000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-73750000</v>
+        <v>-80389000</v>
       </c>
       <c r="AL4" t="n">
-        <v>91062000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>17312000</v>
-      </c>
+        <v>93357000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>84176000</v>
+        <v>86623000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6886000</v>
+        <v>6734000</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>43494000</v>
+        <v>58495000</v>
       </c>
       <c r="AR4" t="n">
-        <v>14570000</v>
+        <v>14757000</v>
       </c>
       <c r="AS4" t="n">
-        <v>17885000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+        <v>22935000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>7476000</v>
+        <v>8921000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-5618000</v>
+        <v>-5220000</v>
       </c>
       <c r="AW4" t="n">
-        <v>13094000</v>
+        <v>14141000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3563000</v>
+        <v>11882000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3563000</v>
+        <v>11882000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3563000</v>
+        <v>11882000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>207507042</v>
+        <v>243052230</v>
       </c>
       <c r="C5" t="n">
-        <v>207507042</v>
+        <v>243052230</v>
       </c>
       <c r="D5" t="n">
-        <v>10473000</v>
+        <v>2304000</v>
       </c>
       <c r="E5" t="n">
-        <v>19922000</v>
+        <v>17101000</v>
       </c>
       <c r="F5" t="n">
-        <v>17295000</v>
+        <v>23880000</v>
       </c>
       <c r="G5" t="n">
-        <v>28267000</v>
+        <v>34704000</v>
       </c>
       <c r="H5" t="n">
-        <v>-2555000</v>
+        <v>16510000</v>
       </c>
       <c r="I5" t="n">
-        <v>17295000</v>
+        <v>23880000</v>
       </c>
       <c r="J5" t="n">
-        <v>8950000</v>
+        <v>6277000</v>
       </c>
       <c r="K5" t="n">
-        <v>17295000</v>
+        <v>23880000</v>
       </c>
       <c r="L5" t="n">
-        <v>17809000</v>
+        <v>23880000</v>
       </c>
       <c r="M5" t="n">
-        <v>17295000</v>
+        <v>23880000</v>
       </c>
       <c r="N5" t="n">
-        <v>17295000</v>
+        <v>23880000</v>
       </c>
       <c r="O5" t="n">
-        <v>-71657000</v>
+        <v>-78876000</v>
       </c>
       <c r="P5" t="n">
-        <v>64575000</v>
+        <v>74347000</v>
       </c>
       <c r="Q5" t="n">
-        <v>8064000</v>
+        <v>12096000</v>
       </c>
       <c r="R5" t="n">
-        <v>8064000</v>
+        <v>12096000</v>
       </c>
       <c r="S5" t="n">
-        <v>57160000</v>
+        <v>38027000</v>
       </c>
       <c r="T5" t="n">
-        <v>5139000</v>
+        <v>3140000</v>
       </c>
       <c r="U5" t="n">
-        <v>818000</v>
+        <v>690000</v>
       </c>
       <c r="V5" t="n">
-        <v>80000</v>
+        <v>650000</v>
       </c>
       <c r="W5" t="n">
-        <v>4241000</v>
+        <v>1800000</v>
       </c>
       <c r="X5" t="n">
-        <v>3727000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>514000</v>
-      </c>
+        <v>1800000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>52021000</v>
+        <v>34887000</v>
       </c>
       <c r="AA5" t="n">
-        <v>15681000</v>
+        <v>15301000</v>
       </c>
       <c r="AB5" t="n">
-        <v>5223000</v>
+        <v>4477000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10458000</v>
+        <v>10824000</v>
       </c>
       <c r="AD5" t="n">
-        <v>21112000</v>
+        <v>12594000</v>
       </c>
       <c r="AE5" t="n">
-        <v>3657000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>342000</v>
-      </c>
+        <v>2612000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>17113000</v>
+        <v>9982000</v>
       </c>
       <c r="AH5" t="n">
-        <v>74455000</v>
+        <v>61907000</v>
       </c>
       <c r="AI5" t="n">
-        <v>24989000</v>
+        <v>10510000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24989000</v>
+        <v>10510000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-65257000</v>
+        <v>-87368000</v>
       </c>
       <c r="AL5" t="n">
-        <v>90246000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>24989000</v>
-      </c>
+        <v>97878000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>84468000</v>
+        <v>91144000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5778000</v>
+        <v>6734000</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>49466000</v>
+        <v>51397000</v>
       </c>
       <c r="AR5" t="n">
-        <v>14559000</v>
+        <v>15259000</v>
       </c>
       <c r="AS5" t="n">
-        <v>20580000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>113000</v>
-      </c>
+        <v>21528000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>13715000</v>
+        <v>6090000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-5420000</v>
+        <v>-5399000</v>
       </c>
       <c r="AW5" t="n">
-        <v>19135000</v>
+        <v>11489000</v>
       </c>
       <c r="AX5" t="n">
-        <v>499000</v>
+        <v>8520000</v>
       </c>
       <c r="AY5" t="n">
-        <v>499000</v>
+        <v>8520000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>499000</v>
+        <v>8520000</v>
       </c>
     </row>
   </sheetData>
@@ -2301,430 +2301,430 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>4004000</v>
+        <v>-20405000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1755000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>-3163000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>21638000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2632000</v>
+        <v>-10532000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1327000</v>
+        <v>-1315000</v>
       </c>
       <c r="H2" t="n">
-        <v>2231000</v>
+        <v>7910000</v>
       </c>
       <c r="I2" t="n">
-        <v>-3558000</v>
+        <v>-9225000</v>
       </c>
       <c r="J2" t="n">
-        <v>-9328000</v>
+        <v>10025000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1503000</v>
+        <v>-1905000</v>
       </c>
       <c r="L2" t="n">
-        <v>-982000</v>
+        <v>-860000</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>21638000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>21638000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1755000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1755000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1755000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>-3163000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-3163000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-3163000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
       <c r="U2" t="n">
-        <v>-866000</v>
+        <v>-9377000</v>
       </c>
       <c r="V2" t="n">
-        <v>814000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>25000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-1680000</v>
+        <v>-9402000</v>
       </c>
       <c r="Z2" t="n">
-        <v>952000</v>
+        <v>1130000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2632000</v>
+        <v>-10532000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6636000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>-9873000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-4945000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-81000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1200000</v>
-      </c>
+        <v>19883000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-6571000</v>
+        <v>-2020000</v>
       </c>
       <c r="AH2" t="n">
-        <v>507000</v>
+        <v>21903000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-53000</v>
+        <v>699000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8319000</v>
+        <v>13700000</v>
       </c>
       <c r="AK2" t="n">
-        <v>8319000</v>
+        <v>13700000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-911000</v>
+        <v>-401000</v>
       </c>
       <c r="AM2" t="n">
-        <v>495000</v>
+        <v>-40904000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3234000</v>
+        <v>4035000</v>
       </c>
       <c r="C3" t="n">
-        <v>-3175000</v>
+        <v>-3251000</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>14919000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-861000</v>
+        <v>-55000</v>
       </c>
       <c r="G3" t="n">
-        <v>2231000</v>
+        <v>-6157000</v>
       </c>
       <c r="H3" t="n">
-        <v>-6157000</v>
+        <v>-1315000</v>
       </c>
       <c r="I3" t="n">
-        <v>8388000</v>
+        <v>-4842000</v>
       </c>
       <c r="J3" t="n">
-        <v>4801000</v>
+        <v>-9048000</v>
       </c>
       <c r="K3" t="n">
-        <v>-536000</v>
+        <v>294000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1070000</v>
+        <v>-869000</v>
       </c>
       <c r="M3" t="n">
-        <v>14919000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>14919000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-3175000</v>
+        <v>-3251000</v>
       </c>
       <c r="P3" t="n">
-        <v>-3175000</v>
+        <v>-3251000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3175000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+        <v>-3251000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-3251000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-3251000</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>-508000</v>
+        <v>116000</v>
       </c>
       <c r="V3" t="n">
-        <v>329000</v>
+        <v>11000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-837000</v>
+        <v>105000</v>
       </c>
       <c r="Z3" t="n">
-        <v>24000</v>
+        <v>160000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-861000</v>
+        <v>-55000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4095000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>4090000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-6599000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
+        <v>-946000</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>-882000</v>
+        <v>-8096000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-5717000</v>
+        <v>7150000</v>
       </c>
       <c r="AI3" t="n">
-        <v>718000</v>
+        <v>607000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9460000</v>
+        <v>12066000</v>
       </c>
       <c r="AK3" t="n">
-        <v>9460000</v>
+        <v>12066000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-24000</v>
+        <v>-160000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1318000</v>
+        <v>-9261000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>4035000</v>
+        <v>3234000</v>
       </c>
       <c r="C4" t="n">
-        <v>-3251000</v>
+        <v>-3175000</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>14919000</v>
       </c>
       <c r="F4" t="n">
-        <v>-55000</v>
+        <v>-861000</v>
       </c>
       <c r="G4" t="n">
+        <v>2231000</v>
+      </c>
+      <c r="H4" t="n">
         <v>-6157000</v>
       </c>
-      <c r="H4" t="n">
-        <v>-1315000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-4842000</v>
+        <v>8388000</v>
       </c>
       <c r="J4" t="n">
-        <v>-9048000</v>
+        <v>4801000</v>
       </c>
       <c r="K4" t="n">
-        <v>294000</v>
+        <v>-536000</v>
       </c>
       <c r="L4" t="n">
-        <v>-869000</v>
+        <v>-1070000</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>14919000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>14919000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3251000</v>
+        <v>-3175000</v>
       </c>
       <c r="P4" t="n">
-        <v>-3251000</v>
+        <v>-3175000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3251000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-3251000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-3251000</v>
-      </c>
+        <v>-3175000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>116000</v>
+        <v>-508000</v>
       </c>
       <c r="V4" t="n">
-        <v>11000</v>
+        <v>329000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>105000</v>
+        <v>-837000</v>
       </c>
       <c r="Z4" t="n">
-        <v>160000</v>
+        <v>24000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-55000</v>
+        <v>-861000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4090000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>4095000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-946000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>-6599000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
       <c r="AG4" t="n">
-        <v>-8096000</v>
+        <v>-882000</v>
       </c>
       <c r="AH4" t="n">
-        <v>7150000</v>
+        <v>-5717000</v>
       </c>
       <c r="AI4" t="n">
-        <v>607000</v>
+        <v>718000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12066000</v>
+        <v>9460000</v>
       </c>
       <c r="AK4" t="n">
-        <v>12066000</v>
+        <v>9460000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-160000</v>
+        <v>-24000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-9261000</v>
+        <v>1318000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-20405000</v>
+        <v>4004000</v>
       </c>
       <c r="C5" t="n">
-        <v>-3163000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1755000</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>21638000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-10532000</v>
+        <v>-2632000</v>
       </c>
       <c r="G5" t="n">
-        <v>-1315000</v>
+        <v>-1327000</v>
       </c>
       <c r="H5" t="n">
-        <v>7910000</v>
+        <v>2231000</v>
       </c>
       <c r="I5" t="n">
-        <v>-9225000</v>
+        <v>-3558000</v>
       </c>
       <c r="J5" t="n">
-        <v>10025000</v>
+        <v>-9328000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1905000</v>
+        <v>-1503000</v>
       </c>
       <c r="L5" t="n">
-        <v>-860000</v>
+        <v>-982000</v>
       </c>
       <c r="M5" t="n">
-        <v>21638000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>21638000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-3163000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>-3163000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-3163000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1755000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1755000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1755000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-9377000</v>
+        <v>-866000</v>
       </c>
       <c r="V5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
+        <v>814000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-9402000</v>
+        <v>-1680000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1130000</v>
+        <v>952000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-10532000</v>
+        <v>-2632000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-9873000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
+        <v>6636000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>19883000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+        <v>-4945000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-81000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1200000</v>
+      </c>
       <c r="AG5" t="n">
-        <v>-2020000</v>
+        <v>-6571000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21903000</v>
+        <v>507000</v>
       </c>
       <c r="AI5" t="n">
-        <v>699000</v>
+        <v>-53000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13700000</v>
+        <v>8319000</v>
       </c>
       <c r="AK5" t="n">
-        <v>13700000</v>
+        <v>8319000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-401000</v>
+        <v>-911000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-40904000</v>
+        <v>495000</v>
       </c>
     </row>
   </sheetData>
@@ -2738,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI2"/>
+  <dimension ref="A1:EG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2764,675 +2764,665 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>website</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>industryKey</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>industryDisp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>industryKey</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>industryDisp</t>
+          <t>sectorKey</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sectorDisp</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>sectorKey</t>
+          <t>longBusinessSummary</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>sectorDisp</t>
+          <t>fullTimeEmployees</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>longBusinessSummary</t>
+          <t>companyOfficers</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>fullTimeEmployees</t>
+          <t>compensationAsOfEpochDate</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>companyOfficers</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>compensationAsOfEpochDate</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>open</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>payoutRatio</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>regularMarketChange</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
       <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3441,17 +3431,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fu Hop Factory Building</t>
+          <t>21 Ashley</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Flat B, G/F 209 and 211 Wai Yip Street</t>
+          <t>Unit 1901, 19/F 21 Ashley Road</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kwun Tong</t>
+          <t>Tsim Sha Tsui</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3461,17 +3451,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>852 2798 9202</t>
+          <t>https://www.aienergy.com.hk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>852 2798 9187</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.aienergy.com.hk</t>
+          <t>engineering-construction</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3481,12 +3471,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>engineering-construction</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>industrials</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3496,442 +3486,432 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>industrials</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
+          <t>AI Energy Engineering Holdings Limited, together with its subsidiaries, provides concrete demolition services primarily as a subcontractor in Hong Kong and Macau. The company removes pieces or sections of concrete from concrete structures; and demolishes concrete structures or buildings through core drilling, sawing, and crushing. Its services are used in various areas, such as addition and alteration works, and redevelopment projects in buildings, roads, tunnels, and underground facilities. The company serves contractors in construction and civil engineering projects in public and private sectors. The company was formerly known as Kingland Group Holdings Limited and changed its name to AI Energy Engineering Holdings Limited in February 2026. AI Energy Engineering Holdings Limited was founded in 1985 and is headquartered in Tsim Sha Tsui, Hong Kong.</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>84</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AI Energy Engineering Holdings Limited, together with its subsidiaries, provides concrete demolition services primarily as a subcontractor in Hong Kong and Macau. The company removes pieces or sections of concrete from concrete structures; and demolishes concrete structures or buildings through core drilling, sawing, and crushing. Its services are used in various areas, such as addition and alteration works, and redevelopment projects in buildings, roads, tunnels, and underground facilities. The company serves contractors in construction and civil engineering projects in public and private sectors. The company was formerly known as Kingland Group Holdings Limited and changed its name to AI Energy Engineering Holdings Limited in February 2026. AI Energy Engineering Holdings Limited was founded in 1985 and is headquartered in Kwun Tong, Hong Kong.</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Yifan  Cao', 'age': 41, 'title': 'CEO &amp; Executive Chairman', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 286000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaoli  Pang', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 4000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yeung Tak  Chen CPA', 'age': 41, 'title': 'Financial Controller &amp; Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 98000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Banna  Mak', 'age': 62, 'title': 'Chief Technical Officer', 'yearBorn': 1963, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Fung Ling  Tsu', 'age': 58, 'title': 'Administrative Manager', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Man  Yip', 'age': 56, 'title': 'Sales Manager', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jia  Su', 'age': 51, 'title': 'Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>84</v>
+        <v>1767139200</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Yifan  Cao', 'age': 41, 'title': 'CEO &amp; Executive Chairman', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 286000, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q2" t="n">
+        <v>86400</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>774364</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>354000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>354000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>378551968</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>355256478</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>46.38333</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.2415776</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.3593903</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="AX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>342585984</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.1571</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>158987405</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>291193835</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.34175998</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>291193835</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>24.999998</v>
+      </c>
+      <c r="BH2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>86400</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1177000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1177000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>823696</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1188828</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1188828</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>346520672</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>337784848</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>46.38333</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.79806</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.414</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.3143653</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="AZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>313555584</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.1571</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>158987405</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>291193835</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.34175998</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>291193835</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.052</v>
-      </c>
       <c r="BI2" t="n">
-        <v>22.884617</v>
+        <v>1798675200</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
       </c>
       <c r="BK2" t="n">
-        <v>1798675200</v>
+        <v>-11346000</v>
       </c>
       <c r="BL2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-11346000</v>
+        <v>-0.05</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1:5</t>
+        </is>
       </c>
       <c r="BN2" t="n">
+        <v>1684454400</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.744</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-38.252</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>2.3888888</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BV2" t="n">
+        <v>1938000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-8956000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>30028000</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>72221000</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>239.572</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-0.10346</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-0.62317</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>18061000</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>2224875</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>-1361000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.12401</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-0.15291001</v>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>1751.HK</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CV2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.07999992</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>1.22 - 1.3</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>774364</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.97999996</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>3.0625</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.32 - 2.38</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-1.0800002</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.45378155</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>238.88889</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1742909458</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1742909458</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>1:5</t>
-        </is>
-      </c>
-      <c r="BP2" t="n">
-        <v>1684454400</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>4.342</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>-35.011</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>2.3714285</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BV2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="BX2" t="n">
-        <v>1938000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-8956000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>30028000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1.086</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>72221000</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>239.572</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>-0.10346</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>-0.62317</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>18061000</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>2224875</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-1361000</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0.25008</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>-0.12401</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>-0.15291001</v>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>1751.HK</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DK2" t="n">
+        <v>-0.042000055</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.031296615</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.059390306</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.04368893</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1482111000000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>AI Energy Engineering Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>6.5573707</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>finmb_61789646</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
-        <v>1780385627</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>finmb_61789646</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>AI Energy Engineering Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EE2" t="n">
+        <v>1782115189</v>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>AI ENERGY ENG</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1482111000000</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.01000011</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>1.17 - 1.3</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>823696</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.87000006</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>2.7187502</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>0.32 - 2.38</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>237.14285</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1742909458</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1742909458</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.22399998</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.15841582</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.12436521</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.094619974</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.8474669500000001</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="EI2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
